--- a/data/base de datos ordenada para procesar.xlsx
+++ b/data/base de datos ordenada para procesar.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fvygh\Documents\TESIS_PREGRADO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fvygh\Documents\TESIS_PREGRADO\Heat map diversidad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19768DB8-D321-4115-9A11-15D6B21DE7B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3146813B-8734-45CC-A1F4-C2A37264F018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="15375" windowHeight="7785" xr2:uid="{354A38B0-6B5E-400C-9BC9-4B52A0F053CA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{354A38B0-6B5E-400C-9BC9-4B52A0F053CA}"/>
   </bookViews>
   <sheets>
     <sheet name="fb" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1417" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="98">
   <si>
     <t>provincia</t>
   </si>
@@ -69,9 +69,6 @@
     <t>tuberculata</t>
   </si>
   <si>
-    <t>lutem</t>
-  </si>
-  <si>
     <t>Septoglomus</t>
   </si>
   <si>
@@ -84,12 +81,6 @@
     <t>Rhizophagus</t>
   </si>
   <si>
-    <t>Rhizoglomus</t>
-  </si>
-  <si>
-    <t>intraradice</t>
-  </si>
-  <si>
     <t>etunicatum</t>
   </si>
   <si>
@@ -120,9 +111,6 @@
     <t>Glomus</t>
   </si>
   <si>
-    <t>Sp1.</t>
-  </si>
-  <si>
     <t>epigaea</t>
   </si>
   <si>
@@ -141,18 +129,12 @@
     <t>CA04</t>
   </si>
   <si>
-    <t>Sp2.</t>
-  </si>
-  <si>
     <t>maculosum</t>
   </si>
   <si>
     <t>spurca</t>
   </si>
   <si>
-    <t>verruculosum</t>
-  </si>
-  <si>
     <t>denticulata</t>
   </si>
   <si>
@@ -201,9 +183,6 @@
     <t>CA14</t>
   </si>
   <si>
-    <t>Cahchapoyas</t>
-  </si>
-  <si>
     <t>CT01</t>
   </si>
   <si>
@@ -219,21 +198,12 @@
     <t>CT03</t>
   </si>
   <si>
-    <t>intrarradices</t>
-  </si>
-  <si>
     <t>CT04</t>
   </si>
   <si>
-    <t>geosporum</t>
-  </si>
-  <si>
     <t>CT05</t>
   </si>
   <si>
-    <t>coronatum</t>
-  </si>
-  <si>
     <t>CT06</t>
   </si>
   <si>
@@ -270,9 +240,6 @@
     <t>gigantea</t>
   </si>
   <si>
-    <t>Denticustata</t>
-  </si>
-  <si>
     <t>erythropus</t>
   </si>
   <si>
@@ -300,33 +267,21 @@
     <t>CT16</t>
   </si>
   <si>
-    <t>lacunnosa</t>
-  </si>
-  <si>
     <t>bireticulata</t>
   </si>
   <si>
     <t>CT18</t>
   </si>
   <si>
-    <t>kentinesis</t>
-  </si>
-  <si>
     <t>CT19</t>
   </si>
   <si>
     <t>CT20</t>
   </si>
   <si>
-    <t>leavis</t>
-  </si>
-  <si>
     <t>CT22</t>
   </si>
   <si>
-    <t>verrucuosa</t>
-  </si>
-  <si>
     <t>CT31</t>
   </si>
   <si>
@@ -343,6 +298,39 @@
   </si>
   <si>
     <t>accesion</t>
+  </si>
+  <si>
+    <t>intraradices</t>
+  </si>
+  <si>
+    <t>luteum</t>
+  </si>
+  <si>
+    <t>sp. 1</t>
+  </si>
+  <si>
+    <t>sp. 2</t>
+  </si>
+  <si>
+    <t>verruculosus</t>
+  </si>
+  <si>
+    <t>geosporus</t>
+  </si>
+  <si>
+    <t>coronatus</t>
+  </si>
+  <si>
+    <t>lacunosa</t>
+  </si>
+  <si>
+    <t>Dentiscutata</t>
+  </si>
+  <si>
+    <t>kentinensis</t>
+  </si>
+  <si>
+    <t>verrucosa</t>
   </si>
 </sst>
 </file>
@@ -384,8 +372,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -700,17 +689,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CFAA758-8801-4B5D-9100-C94A23A9D13F}">
-  <dimension ref="A1:G236"/>
+  <dimension ref="A1:G234"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -719,12 +708,12 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G1" t="s">
@@ -733,7 +722,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -747,7 +736,7 @@
       <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G2">
@@ -756,7 +745,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -770,8 +759,8 @@
       <c r="E3" t="s">
         <v>8</v>
       </c>
-      <c r="F3" t="s">
-        <v>43</v>
+      <c r="F3" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G3">
         <v>58</v>
@@ -779,7 +768,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
@@ -791,10 +780,10 @@
         <v>7</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
+        <v>17</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="G4">
         <v>42</v>
@@ -802,7 +791,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
@@ -814,10 +803,10 @@
         <v>7</v>
       </c>
       <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
       </c>
       <c r="G5">
         <v>128</v>
@@ -825,7 +814,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B6" t="s">
         <v>5</v>
@@ -837,10 +826,10 @@
         <v>7</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" t="s">
         <v>13</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="G6">
         <v>19</v>
@@ -848,7 +837,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
         <v>5</v>
@@ -860,10 +849,10 @@
         <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" t="s">
-        <v>60</v>
+        <v>13</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="G7">
         <v>12</v>
@@ -871,7 +860,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
@@ -883,10 +872,10 @@
         <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" t="s">
         <v>17</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G8">
         <v>120</v>
@@ -894,7 +883,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
         <v>5</v>
@@ -903,21 +892,21 @@
         <v>6</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" t="s">
         <v>17</v>
       </c>
+      <c r="F9" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="G9">
-        <v>95</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B10" t="s">
         <v>5</v>
@@ -926,13 +915,13 @@
         <v>6</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" t="s">
-        <v>22</v>
+        <v>18</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G10">
         <v>198</v>
@@ -940,7 +929,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
         <v>5</v>
@@ -949,13 +938,13 @@
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
-      <c r="F11" t="s">
-        <v>23</v>
+      <c r="F11" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="G11">
         <v>72</v>
@@ -963,7 +952,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
         <v>5</v>
@@ -972,21 +961,21 @@
         <v>6</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" t="s">
         <v>17</v>
       </c>
+      <c r="F12" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G12">
-        <v>239</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
         <v>5</v>
@@ -995,21 +984,21 @@
         <v>6</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>20</v>
-      </c>
-      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G13">
-        <v>145</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B14" t="s">
         <v>5</v>
@@ -1018,21 +1007,21 @@
         <v>6</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" t="s">
-        <v>29</v>
+        <v>13</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="G14">
-        <v>128</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B15" t="s">
         <v>5</v>
@@ -1041,21 +1030,21 @@
         <v>6</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" t="s">
-        <v>13</v>
+        <v>18</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="G15">
-        <v>18</v>
+        <v>344</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B16" t="s">
         <v>5</v>
@@ -1064,21 +1053,21 @@
         <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" t="s">
-        <v>24</v>
+        <v>18</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="G16">
-        <v>344</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B17" t="s">
         <v>5</v>
@@ -1087,21 +1076,21 @@
         <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E17" t="s">
-        <v>21</v>
-      </c>
-      <c r="F17" t="s">
-        <v>32</v>
+        <v>23</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="G17">
-        <v>37</v>
+        <v>285</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B18" t="s">
         <v>5</v>
@@ -1110,21 +1099,21 @@
         <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>26</v>
-      </c>
-      <c r="F18" t="s">
-        <v>27</v>
+        <v>18</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G18">
-        <v>285</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B19" t="s">
         <v>5</v>
@@ -1133,21 +1122,21 @@
         <v>6</v>
       </c>
       <c r="D19" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E19" t="s">
-        <v>21</v>
-      </c>
-      <c r="F19" t="s">
-        <v>28</v>
+        <v>23</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="G19">
-        <v>84</v>
+        <v>297</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B20" t="s">
         <v>5</v>
@@ -1156,21 +1145,21 @@
         <v>6</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E20" t="s">
-        <v>26</v>
-      </c>
-      <c r="F20" t="s">
-        <v>30</v>
+        <v>13</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="G20">
-        <v>297</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B21" t="s">
         <v>5</v>
@@ -1179,21 +1168,21 @@
         <v>6</v>
       </c>
       <c r="D21" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E21" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" t="s">
-        <v>31</v>
-      </c>
       <c r="G21">
-        <v>40</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B22" t="s">
         <v>5</v>
@@ -1202,21 +1191,21 @@
         <v>6</v>
       </c>
       <c r="D22" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F22" t="s">
-        <v>22</v>
-      </c>
       <c r="G22">
-        <v>95</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B23" t="s">
         <v>5</v>
@@ -1225,21 +1214,21 @@
         <v>6</v>
       </c>
       <c r="D23" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E23" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" t="s">
-        <v>24</v>
+        <v>18</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="G23">
-        <v>199</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B24" t="s">
         <v>5</v>
@@ -1248,21 +1237,21 @@
         <v>6</v>
       </c>
       <c r="D24" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E24" t="s">
-        <v>21</v>
-      </c>
-      <c r="F24" t="s">
-        <v>32</v>
+        <v>18</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G24">
-        <v>128</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B25" t="s">
         <v>5</v>
@@ -1271,21 +1260,21 @@
         <v>6</v>
       </c>
       <c r="D25" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E25" t="s">
-        <v>21</v>
-      </c>
-      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G25">
-        <v>101</v>
+        <v>487</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B26" t="s">
         <v>5</v>
@@ -1294,21 +1283,21 @@
         <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E26" t="s">
-        <v>21</v>
-      </c>
-      <c r="F26" t="s">
-        <v>32</v>
+        <v>23</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="G26">
-        <v>487</v>
+        <v>311</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B27" t="s">
         <v>5</v>
@@ -1317,21 +1306,21 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E27" t="s">
-        <v>26</v>
-      </c>
-      <c r="F27" t="s">
-        <v>34</v>
+        <v>23</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="G27">
-        <v>311</v>
+        <v>152</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B28" t="s">
         <v>5</v>
@@ -1340,21 +1329,21 @@
         <v>6</v>
       </c>
       <c r="D28" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E28" t="s">
-        <v>26</v>
-      </c>
-      <c r="F28" t="s">
-        <v>35</v>
+        <v>13</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="G28">
-        <v>152</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B29" t="s">
         <v>5</v>
@@ -1363,21 +1352,21 @@
         <v>6</v>
       </c>
       <c r="D29" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E29" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F29" t="s">
-        <v>13</v>
-      </c>
       <c r="G29">
-        <v>112</v>
+        <v>334</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B30" t="s">
         <v>5</v>
@@ -1386,21 +1375,21 @@
         <v>6</v>
       </c>
       <c r="D30" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E30" t="s">
-        <v>20</v>
-      </c>
-      <c r="F30" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="G30">
-        <v>334</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B31" t="s">
         <v>5</v>
@@ -1409,21 +1398,21 @@
         <v>6</v>
       </c>
       <c r="D31" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E31" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" t="s">
-        <v>36</v>
+        <v>58</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="G31">
-        <v>59</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B32" t="s">
         <v>5</v>
@@ -1432,21 +1421,21 @@
         <v>6</v>
       </c>
       <c r="D32" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E32" t="s">
-        <v>68</v>
-      </c>
-      <c r="F32" t="s">
-        <v>37</v>
+        <v>13</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="G32">
-        <v>110</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B33" t="s">
         <v>5</v>
@@ -1455,21 +1444,21 @@
         <v>6</v>
       </c>
       <c r="D33" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E33" t="s">
-        <v>14</v>
-      </c>
-      <c r="F33" t="s">
-        <v>31</v>
+        <v>8</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="G33">
-        <v>195</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B34" t="s">
         <v>5</v>
@@ -1481,18 +1470,18 @@
         <v>33</v>
       </c>
       <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" t="s">
-        <v>38</v>
+        <v>18</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G34">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B35" t="s">
         <v>5</v>
@@ -1501,21 +1490,21 @@
         <v>6</v>
       </c>
       <c r="D35" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E35" t="s">
-        <v>21</v>
-      </c>
-      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G35">
-        <v>72</v>
+        <v>232</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B36" t="s">
         <v>5</v>
@@ -1524,21 +1513,21 @@
         <v>6</v>
       </c>
       <c r="D36" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E36" t="s">
-        <v>21</v>
-      </c>
-      <c r="F36" t="s">
-        <v>32</v>
+        <v>17</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G36">
-        <v>232</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B37" t="s">
         <v>5</v>
@@ -1547,21 +1536,21 @@
         <v>6</v>
       </c>
       <c r="D37" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E37" t="s">
-        <v>20</v>
-      </c>
-      <c r="F37" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G37">
-        <v>95</v>
+        <v>263</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B38" t="s">
         <v>5</v>
@@ -1570,21 +1559,21 @@
         <v>6</v>
       </c>
       <c r="D38" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E38" t="s">
-        <v>21</v>
-      </c>
-      <c r="F38" t="s">
-        <v>28</v>
+        <v>8</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="G38">
-        <v>263</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B39" t="s">
         <v>5</v>
@@ -1593,21 +1582,21 @@
         <v>6</v>
       </c>
       <c r="D39" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>41</v>
+        <v>58</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="G39">
-        <v>67</v>
+        <v>54</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B40" t="s">
         <v>5</v>
@@ -1616,21 +1605,21 @@
         <v>6</v>
       </c>
       <c r="D40" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E40" t="s">
-        <v>68</v>
-      </c>
-      <c r="F40" t="s">
-        <v>37</v>
+        <v>18</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="G40">
-        <v>54</v>
+        <v>391</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B41" t="s">
         <v>5</v>
@@ -1639,21 +1628,21 @@
         <v>6</v>
       </c>
       <c r="D41" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E41" t="s">
-        <v>21</v>
-      </c>
-      <c r="F41" t="s">
-        <v>32</v>
+        <v>13</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="G41">
-        <v>391</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B42" t="s">
         <v>5</v>
@@ -1662,21 +1651,21 @@
         <v>6</v>
       </c>
       <c r="D42" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E42" t="s">
-        <v>14</v>
-      </c>
-      <c r="F42" t="s">
-        <v>44</v>
+        <v>23</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="G42">
-        <v>27</v>
+        <v>138</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B43" t="s">
         <v>5</v>
@@ -1685,21 +1674,21 @@
         <v>6</v>
       </c>
       <c r="D43" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E43" t="s">
-        <v>26</v>
-      </c>
-      <c r="F43" t="s">
-        <v>35</v>
+        <v>17</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G43">
-        <v>138</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B44" t="s">
         <v>5</v>
@@ -1708,21 +1697,21 @@
         <v>6</v>
       </c>
       <c r="D44" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E44" t="s">
-        <v>20</v>
-      </c>
-      <c r="F44" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G44">
-        <v>109</v>
+        <v>205</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B45" t="s">
         <v>5</v>
@@ -1731,21 +1720,21 @@
         <v>6</v>
       </c>
       <c r="D45" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E45" t="s">
-        <v>21</v>
-      </c>
-      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G45">
-        <v>205</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B46" t="s">
         <v>5</v>
@@ -1754,21 +1743,21 @@
         <v>6</v>
       </c>
       <c r="D46" t="s">
+        <v>36</v>
+      </c>
+      <c r="E46" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G46">
         <v>42</v>
-      </c>
-      <c r="E46" t="s">
-        <v>21</v>
-      </c>
-      <c r="F46" t="s">
-        <v>32</v>
-      </c>
-      <c r="G46">
-        <v>66</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B47" t="s">
         <v>5</v>
@@ -1777,21 +1766,21 @@
         <v>6</v>
       </c>
       <c r="D47" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E47" t="s">
+        <v>17</v>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F47" t="s">
-        <v>29</v>
-      </c>
       <c r="G47">
-        <v>42</v>
+        <v>224</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B48" t="s">
         <v>5</v>
@@ -1800,21 +1789,21 @@
         <v>6</v>
       </c>
       <c r="D48" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E48" t="s">
-        <v>20</v>
-      </c>
-      <c r="F48" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G48">
-        <v>224</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B49" t="s">
         <v>5</v>
@@ -1823,21 +1812,21 @@
         <v>6</v>
       </c>
       <c r="D49" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E49" t="s">
-        <v>21</v>
-      </c>
-      <c r="F49" t="s">
-        <v>28</v>
+        <v>8</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="G49">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B50" t="s">
         <v>5</v>
@@ -1846,21 +1835,21 @@
         <v>6</v>
       </c>
       <c r="D50" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E50" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" t="s">
-        <v>38</v>
+        <v>23</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="G50">
-        <v>14</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B51" t="s">
         <v>5</v>
@@ -1869,21 +1858,21 @@
         <v>6</v>
       </c>
       <c r="D51" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E51" t="s">
-        <v>26</v>
-      </c>
-      <c r="F51" t="s">
-        <v>35</v>
+        <v>13</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="G51">
-        <v>33</v>
+        <v>64</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B52" t="s">
         <v>5</v>
@@ -1892,21 +1881,21 @@
         <v>6</v>
       </c>
       <c r="D52" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E52" t="s">
-        <v>14</v>
-      </c>
-      <c r="F52" t="s">
-        <v>31</v>
+        <v>13</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="G52">
-        <v>64</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B53" t="s">
         <v>5</v>
@@ -1915,21 +1904,21 @@
         <v>6</v>
       </c>
       <c r="D53" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E53" t="s">
-        <v>14</v>
-      </c>
-      <c r="F53" t="s">
-        <v>29</v>
+        <v>18</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="G53">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B54" t="s">
         <v>5</v>
@@ -1938,21 +1927,21 @@
         <v>6</v>
       </c>
       <c r="D54" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E54" t="s">
-        <v>21</v>
-      </c>
-      <c r="F54" t="s">
-        <v>32</v>
+        <v>18</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="G54">
-        <v>84</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B55" t="s">
         <v>5</v>
@@ -1961,21 +1950,21 @@
         <v>6</v>
       </c>
       <c r="D55" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E55" t="s">
-        <v>21</v>
-      </c>
-      <c r="F55" t="s">
-        <v>32</v>
+        <v>17</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G55">
-        <v>38</v>
+        <v>172</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B56" t="s">
         <v>5</v>
@@ -1984,21 +1973,21 @@
         <v>6</v>
       </c>
       <c r="D56" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E56" t="s">
-        <v>20</v>
-      </c>
-      <c r="F56" t="s">
-        <v>17</v>
+        <v>10</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="G56">
-        <v>172</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B57" t="s">
         <v>5</v>
@@ -2007,21 +1996,21 @@
         <v>6</v>
       </c>
       <c r="D57" t="s">
+        <v>40</v>
+      </c>
+      <c r="E57" t="s">
+        <v>23</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G57">
         <v>46</v>
-      </c>
-      <c r="E57" t="s">
-        <v>11</v>
-      </c>
-      <c r="F57" t="s">
-        <v>12</v>
-      </c>
-      <c r="G57">
-        <v>16</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B58" t="s">
         <v>5</v>
@@ -2030,21 +2019,21 @@
         <v>6</v>
       </c>
       <c r="D58" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E58" t="s">
-        <v>26</v>
-      </c>
-      <c r="F58" t="s">
-        <v>35</v>
+        <v>18</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G58">
-        <v>46</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B59" t="s">
         <v>5</v>
@@ -2053,21 +2042,21 @@
         <v>6</v>
       </c>
       <c r="D59" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E59" t="s">
-        <v>21</v>
-      </c>
-      <c r="F59" t="s">
-        <v>28</v>
+        <v>8</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="G59">
-        <v>21</v>
+        <v>120</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B60" t="s">
         <v>5</v>
@@ -2076,21 +2065,21 @@
         <v>6</v>
       </c>
       <c r="D60" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E60" t="s">
-        <v>8</v>
-      </c>
-      <c r="F60" t="s">
-        <v>41</v>
+        <v>17</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G60">
-        <v>120</v>
+        <v>82</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B61" t="s">
         <v>5</v>
@@ -2099,21 +2088,21 @@
         <v>6</v>
       </c>
       <c r="D61" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E61" t="s">
-        <v>20</v>
-      </c>
-      <c r="F61" t="s">
-        <v>17</v>
+        <v>23</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="G61">
-        <v>82</v>
+        <v>98</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B62" t="s">
         <v>5</v>
@@ -2122,21 +2111,21 @@
         <v>6</v>
       </c>
       <c r="D62" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E62" t="s">
-        <v>26</v>
-      </c>
-      <c r="F62" t="s">
-        <v>35</v>
+        <v>13</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G62">
-        <v>98</v>
+        <v>124</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B63" t="s">
         <v>5</v>
@@ -2145,21 +2134,21 @@
         <v>6</v>
       </c>
       <c r="D63" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E63" t="s">
-        <v>14</v>
-      </c>
-      <c r="F63" t="s">
-        <v>48</v>
+        <v>18</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="G63">
-        <v>124</v>
+        <v>83</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B64" t="s">
         <v>5</v>
@@ -2168,21 +2157,21 @@
         <v>6</v>
       </c>
       <c r="D64" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E64" t="s">
-        <v>21</v>
-      </c>
-      <c r="F64" t="s">
-        <v>32</v>
+        <v>18</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G64">
-        <v>83</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B65" t="s">
         <v>5</v>
@@ -2191,21 +2180,21 @@
         <v>6</v>
       </c>
       <c r="D65" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E65" t="s">
-        <v>21</v>
-      </c>
-      <c r="F65" t="s">
-        <v>28</v>
+        <v>13</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="G65">
-        <v>140</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B66" t="s">
         <v>5</v>
@@ -2214,21 +2203,21 @@
         <v>6</v>
       </c>
       <c r="D66" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E66" t="s">
-        <v>14</v>
-      </c>
-      <c r="F66" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="G66">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B67" t="s">
         <v>5</v>
@@ -2237,21 +2226,21 @@
         <v>6</v>
       </c>
       <c r="D67" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E67" t="s">
-        <v>21</v>
-      </c>
-      <c r="F67" t="s">
-        <v>36</v>
+        <v>17</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="G67">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B68" t="s">
         <v>5</v>
@@ -2260,21 +2249,21 @@
         <v>6</v>
       </c>
       <c r="D68" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E68" t="s">
-        <v>20</v>
-      </c>
-      <c r="F68" t="s">
-        <v>50</v>
+        <v>10</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="G68">
-        <v>33</v>
+        <v>68</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B69" t="s">
         <v>5</v>
@@ -2283,21 +2272,21 @@
         <v>6</v>
       </c>
       <c r="D69" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E69" t="s">
-        <v>11</v>
-      </c>
-      <c r="F69" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="G69">
-        <v>68</v>
+        <v>196</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B70" t="s">
         <v>5</v>
@@ -2306,21 +2295,21 @@
         <v>6</v>
       </c>
       <c r="D70" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E70" t="s">
-        <v>21</v>
-      </c>
-      <c r="F70" t="s">
-        <v>32</v>
+        <v>10</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="G70">
-        <v>196</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B71" t="s">
         <v>5</v>
@@ -2329,21 +2318,21 @@
         <v>6</v>
       </c>
       <c r="D71" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E71" t="s">
-        <v>11</v>
-      </c>
-      <c r="F71" t="s">
-        <v>51</v>
+        <v>18</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="G71">
-        <v>22</v>
+        <v>85</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B72" t="s">
         <v>5</v>
@@ -2352,21 +2341,21 @@
         <v>6</v>
       </c>
       <c r="D72" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E72" t="s">
-        <v>21</v>
-      </c>
-      <c r="F72" t="s">
-        <v>32</v>
+        <v>17</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="G72">
-        <v>85</v>
+        <v>145</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B73" t="s">
         <v>5</v>
@@ -2375,21 +2364,21 @@
         <v>6</v>
       </c>
       <c r="D73" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E73" t="s">
-        <v>20</v>
-      </c>
-      <c r="F73" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="G73">
-        <v>145</v>
+        <v>29</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B74" t="s">
         <v>5</v>
@@ -2398,21 +2387,21 @@
         <v>6</v>
       </c>
       <c r="D74" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E74" t="s">
-        <v>14</v>
-      </c>
-      <c r="F74" t="s">
-        <v>29</v>
+        <v>18</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="G74">
-        <v>29</v>
+        <v>201</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B75" t="s">
         <v>5</v>
@@ -2421,21 +2410,21 @@
         <v>6</v>
       </c>
       <c r="D75" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E75" t="s">
-        <v>21</v>
-      </c>
-      <c r="F75" t="s">
-        <v>32</v>
+        <v>17</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G75">
-        <v>201</v>
+        <v>23</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B76" t="s">
         <v>5</v>
@@ -2444,21 +2433,21 @@
         <v>6</v>
       </c>
       <c r="D76" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E76" t="s">
-        <v>20</v>
-      </c>
-      <c r="F76" t="s">
         <v>17</v>
       </c>
+      <c r="F76" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="G76">
-        <v>23</v>
+        <v>69</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B77" t="s">
         <v>5</v>
@@ -2467,21 +2456,21 @@
         <v>6</v>
       </c>
       <c r="D77" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E77" t="s">
-        <v>20</v>
-      </c>
-      <c r="F77" t="s">
-        <v>50</v>
+        <v>13</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="G77">
-        <v>69</v>
+        <v>46</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="B78" t="s">
         <v>5</v>
@@ -2490,3649 +2479,3603 @@
         <v>6</v>
       </c>
       <c r="D78" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E78" t="s">
-        <v>14</v>
-      </c>
-      <c r="F78" t="s">
-        <v>31</v>
+        <v>8</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="G78">
-        <v>46</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B79" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C79" t="s">
         <v>6</v>
       </c>
       <c r="D79" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E79" t="s">
-        <v>8</v>
-      </c>
-      <c r="F79" t="s">
-        <v>9</v>
+        <v>58</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="G79">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C80" t="s">
         <v>6</v>
       </c>
       <c r="D80" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E80" t="s">
-        <v>68</v>
-      </c>
-      <c r="F80" t="s">
-        <v>37</v>
+        <v>17</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="G80">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B81" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C81" t="s">
         <v>6</v>
       </c>
       <c r="D81" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E81" t="s">
-        <v>20</v>
-      </c>
-      <c r="F81" t="s">
-        <v>50</v>
+        <v>17</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G81">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B82" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C82" t="s">
         <v>6</v>
       </c>
       <c r="D82" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E82" t="s">
+        <v>8</v>
+      </c>
+      <c r="F82" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F82" t="s">
-        <v>17</v>
-      </c>
       <c r="G82">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B83" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C83" t="s">
         <v>6</v>
       </c>
       <c r="D83" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E83" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" t="s">
-        <v>23</v>
+        <v>17</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="G83">
-        <v>8</v>
+        <v>86</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C84" t="s">
         <v>6</v>
       </c>
       <c r="D84" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E84" t="s">
-        <v>20</v>
-      </c>
-      <c r="F84" t="s">
-        <v>25</v>
+        <v>18</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="G84">
-        <v>86</v>
+        <v>37</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B85" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C85" t="s">
         <v>6</v>
       </c>
       <c r="D85" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E85" t="s">
-        <v>21</v>
-      </c>
-      <c r="F85" t="s">
-        <v>32</v>
+        <v>10</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="G85">
-        <v>37</v>
+        <v>75</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C86" t="s">
         <v>6</v>
       </c>
       <c r="D86" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E86" t="s">
-        <v>11</v>
-      </c>
-      <c r="F86" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G86">
-        <v>75</v>
+        <v>758</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C87" t="s">
         <v>6</v>
       </c>
       <c r="D87" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E87" t="s">
-        <v>14</v>
-      </c>
-      <c r="F87" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="G87">
-        <v>758</v>
+        <v>148</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B88" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C88" t="s">
         <v>6</v>
       </c>
       <c r="D88" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E88" t="s">
-        <v>11</v>
-      </c>
-      <c r="F88" t="s">
-        <v>51</v>
+        <v>8</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="G88">
-        <v>148</v>
+        <v>279</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B89" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C89" t="s">
         <v>6</v>
       </c>
       <c r="D89" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E89" t="s">
-        <v>8</v>
-      </c>
-      <c r="F89" t="s">
-        <v>57</v>
+        <v>18</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G89">
-        <v>279</v>
+        <v>204</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B90" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C90" t="s">
         <v>6</v>
       </c>
       <c r="D90" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E90" t="s">
-        <v>21</v>
-      </c>
-      <c r="F90" t="s">
-        <v>28</v>
+        <v>8</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="G90">
-        <v>204</v>
+        <v>231</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B91" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C91" t="s">
         <v>6</v>
       </c>
       <c r="D91" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E91" t="s">
-        <v>8</v>
-      </c>
-      <c r="F91" t="s">
-        <v>58</v>
+        <v>17</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="G91">
-        <v>231</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B92" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C92" t="s">
         <v>6</v>
       </c>
       <c r="D92" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E92" t="s">
-        <v>20</v>
-      </c>
-      <c r="F92" t="s">
-        <v>50</v>
+        <v>18</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G92">
-        <v>19</v>
+        <v>446</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B93" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C93" t="s">
         <v>6</v>
       </c>
       <c r="D93" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E93" t="s">
-        <v>21</v>
-      </c>
-      <c r="F93" t="s">
-        <v>28</v>
+        <v>8</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="G93">
-        <v>446</v>
+        <v>370</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B94" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C94" t="s">
         <v>6</v>
       </c>
       <c r="D94" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E94" t="s">
-        <v>8</v>
-      </c>
-      <c r="F94" t="s">
-        <v>93</v>
+        <v>10</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="G94">
-        <v>370</v>
+        <v>219</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B95" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C95" t="s">
         <v>6</v>
       </c>
       <c r="D95" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E95" t="s">
-        <v>11</v>
-      </c>
-      <c r="F95" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="G95">
-        <v>219</v>
+        <v>461</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B96" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C96" t="s">
         <v>6</v>
       </c>
       <c r="D96" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E96" t="s">
-        <v>14</v>
-      </c>
-      <c r="F96" t="s">
-        <v>60</v>
+        <v>18</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G96">
-        <v>461</v>
+        <v>280</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B97" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C97" t="s">
         <v>6</v>
       </c>
       <c r="D97" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E97" t="s">
-        <v>21</v>
-      </c>
-      <c r="F97" t="s">
-        <v>28</v>
+        <v>58</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="G97">
-        <v>280</v>
+        <v>131</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B98" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C98" t="s">
         <v>6</v>
       </c>
       <c r="D98" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E98" t="s">
-        <v>68</v>
-      </c>
-      <c r="F98" t="s">
-        <v>62</v>
+        <v>13</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="G98">
-        <v>131</v>
+        <v>187</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B99" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C99" t="s">
         <v>6</v>
       </c>
       <c r="D99" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E99" t="s">
-        <v>14</v>
-      </c>
-      <c r="F99" t="s">
-        <v>60</v>
+        <v>23</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="G99">
-        <v>187</v>
+        <v>251</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B100" t="s">
+        <v>5</v>
+      </c>
+      <c r="C100" t="s">
+        <v>6</v>
+      </c>
+      <c r="D100" t="s">
         <v>54</v>
       </c>
-      <c r="C100" t="s">
-        <v>6</v>
-      </c>
-      <c r="D100" t="s">
-        <v>61</v>
-      </c>
       <c r="E100" t="s">
-        <v>26</v>
-      </c>
-      <c r="F100" t="s">
-        <v>35</v>
+        <v>17</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G100">
-        <v>251</v>
+        <v>243</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B101" t="s">
+        <v>5</v>
+      </c>
+      <c r="C101" t="s">
+        <v>6</v>
+      </c>
+      <c r="D101" t="s">
         <v>54</v>
       </c>
-      <c r="C101" t="s">
-        <v>6</v>
-      </c>
-      <c r="D101" t="s">
-        <v>63</v>
-      </c>
       <c r="E101" t="s">
-        <v>20</v>
-      </c>
-      <c r="F101" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G101">
-        <v>243</v>
+        <v>256</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B102" t="s">
+        <v>5</v>
+      </c>
+      <c r="C102" t="s">
+        <v>6</v>
+      </c>
+      <c r="D102" t="s">
         <v>54</v>
       </c>
-      <c r="C102" t="s">
-        <v>6</v>
-      </c>
-      <c r="D102" t="s">
-        <v>63</v>
-      </c>
       <c r="E102" t="s">
-        <v>21</v>
-      </c>
-      <c r="F102" t="s">
-        <v>28</v>
+        <v>8</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="G102">
-        <v>256</v>
+        <v>49</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B103" t="s">
+        <v>5</v>
+      </c>
+      <c r="C103" t="s">
+        <v>6</v>
+      </c>
+      <c r="D103" t="s">
         <v>54</v>
       </c>
-      <c r="C103" t="s">
-        <v>6</v>
-      </c>
-      <c r="D103" t="s">
-        <v>63</v>
-      </c>
       <c r="E103" t="s">
-        <v>8</v>
-      </c>
-      <c r="F103" t="s">
-        <v>38</v>
+        <v>18</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="G103">
-        <v>49</v>
+        <v>156</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B104" t="s">
+        <v>5</v>
+      </c>
+      <c r="C104" t="s">
+        <v>6</v>
+      </c>
+      <c r="D104" t="s">
         <v>54</v>
       </c>
-      <c r="C104" t="s">
-        <v>6</v>
-      </c>
-      <c r="D104" t="s">
-        <v>63</v>
-      </c>
       <c r="E104" t="s">
-        <v>21</v>
-      </c>
-      <c r="F104" t="s">
-        <v>24</v>
+        <v>10</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="G104">
-        <v>156</v>
+        <v>75</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B105" t="s">
+        <v>5</v>
+      </c>
+      <c r="C105" t="s">
+        <v>6</v>
+      </c>
+      <c r="D105" t="s">
         <v>54</v>
       </c>
-      <c r="C105" t="s">
-        <v>6</v>
-      </c>
-      <c r="D105" t="s">
-        <v>63</v>
-      </c>
       <c r="E105" t="s">
-        <v>11</v>
-      </c>
-      <c r="F105" t="s">
-        <v>12</v>
+        <v>58</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="G105">
-        <v>75</v>
+        <v>44</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B106" t="s">
+        <v>5</v>
+      </c>
+      <c r="C106" t="s">
+        <v>6</v>
+      </c>
+      <c r="D106" t="s">
         <v>54</v>
       </c>
-      <c r="C106" t="s">
-        <v>6</v>
-      </c>
-      <c r="D106" t="s">
-        <v>63</v>
-      </c>
       <c r="E106" t="s">
-        <v>68</v>
-      </c>
-      <c r="F106" t="s">
-        <v>64</v>
+        <v>13</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="G106">
-        <v>44</v>
+        <v>357</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B107" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C107" t="s">
         <v>6</v>
       </c>
       <c r="D107" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E107" t="s">
-        <v>14</v>
-      </c>
-      <c r="F107" t="s">
-        <v>13</v>
+        <v>58</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="G107">
-        <v>357</v>
+        <v>302</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B108" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C108" t="s">
         <v>6</v>
       </c>
       <c r="D108" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E108" t="s">
-        <v>68</v>
-      </c>
-      <c r="F108" t="s">
-        <v>66</v>
+        <v>8</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="G108">
-        <v>302</v>
+        <v>198</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B109" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C109" t="s">
         <v>6</v>
       </c>
       <c r="D109" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E109" t="s">
-        <v>8</v>
-      </c>
-      <c r="F109" t="s">
-        <v>9</v>
+        <v>13</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="G109">
-        <v>198</v>
+        <v>262</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B110" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C110" t="s">
         <v>6</v>
       </c>
       <c r="D110" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E110" t="s">
-        <v>14</v>
-      </c>
-      <c r="F110" t="s">
         <v>13</v>
       </c>
+      <c r="F110" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="G110">
-        <v>262</v>
+        <v>76</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B111" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C111" t="s">
         <v>6</v>
       </c>
       <c r="D111" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E111" t="s">
-        <v>14</v>
-      </c>
-      <c r="F111" t="s">
-        <v>29</v>
+        <v>18</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G111">
-        <v>76</v>
+        <v>21</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B112" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C112" t="s">
         <v>6</v>
       </c>
       <c r="D112" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E112" t="s">
-        <v>21</v>
-      </c>
-      <c r="F112" t="s">
-        <v>28</v>
+        <v>13</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="G112">
-        <v>21</v>
+        <v>77</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B113" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C113" t="s">
         <v>6</v>
       </c>
       <c r="D113" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E113" t="s">
-        <v>14</v>
-      </c>
-      <c r="F113" t="s">
-        <v>31</v>
+        <v>58</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="G113">
-        <v>77</v>
+        <v>103</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B114" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C114" t="s">
         <v>6</v>
       </c>
       <c r="D114" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E114" t="s">
-        <v>68</v>
-      </c>
-      <c r="F114" t="s">
-        <v>37</v>
+        <v>8</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="G114">
-        <v>103</v>
+        <v>9</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B115" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C115" t="s">
         <v>6</v>
       </c>
       <c r="D115" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E115" t="s">
-        <v>8</v>
-      </c>
-      <c r="F115" t="s">
-        <v>38</v>
+        <v>17</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="G115">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B116" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C116" t="s">
         <v>6</v>
       </c>
       <c r="D116" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E116" t="s">
-        <v>20</v>
-      </c>
-      <c r="F116" t="s">
-        <v>50</v>
+        <v>58</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="G116">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B117" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C117" t="s">
         <v>6</v>
       </c>
       <c r="D117" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E117" t="s">
-        <v>68</v>
-      </c>
-      <c r="F117" t="s">
-        <v>62</v>
+        <v>18</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G117">
-        <v>42</v>
+        <v>190</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B118" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C118" t="s">
         <v>6</v>
       </c>
       <c r="D118" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E118" t="s">
-        <v>21</v>
-      </c>
-      <c r="F118" t="s">
-        <v>28</v>
+        <v>8</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G118">
-        <v>190</v>
+        <v>39</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B119" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C119" t="s">
         <v>6</v>
       </c>
       <c r="D119" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E119" t="s">
-        <v>8</v>
-      </c>
-      <c r="F119" t="s">
-        <v>43</v>
+        <v>13</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="G119">
-        <v>39</v>
+        <v>117</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B120" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C120" t="s">
         <v>6</v>
       </c>
       <c r="D120" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E120" t="s">
-        <v>14</v>
-      </c>
-      <c r="F120" t="s">
         <v>13</v>
       </c>
+      <c r="F120" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="G120">
-        <v>117</v>
+        <v>41</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B121" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C121" t="s">
         <v>6</v>
       </c>
       <c r="D121" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E121" t="s">
-        <v>14</v>
-      </c>
-      <c r="F121" t="s">
-        <v>31</v>
+        <v>60</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="G121">
-        <v>41</v>
+        <v>12</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B122" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C122" t="s">
         <v>6</v>
       </c>
       <c r="D122" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E122" t="s">
-        <v>70</v>
-      </c>
-      <c r="F122" t="s">
-        <v>71</v>
+        <v>8</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="G122">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B123" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C123" t="s">
         <v>6</v>
       </c>
       <c r="D123" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E123" t="s">
-        <v>8</v>
-      </c>
-      <c r="F123" t="s">
-        <v>72</v>
+        <v>18</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="G123">
-        <v>37</v>
+        <v>125</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B124" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C124" t="s">
         <v>6</v>
       </c>
       <c r="D124" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E124" t="s">
-        <v>21</v>
-      </c>
-      <c r="F124" t="s">
-        <v>27</v>
+        <v>17</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="G124">
-        <v>125</v>
+        <v>46</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B125" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C125" t="s">
         <v>6</v>
       </c>
       <c r="D125" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E125" t="s">
-        <v>20</v>
-      </c>
-      <c r="F125" t="s">
-        <v>25</v>
+        <v>8</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="G125">
-        <v>46</v>
+        <v>87</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B126" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C126" t="s">
         <v>6</v>
       </c>
       <c r="D126" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E126" t="s">
-        <v>8</v>
-      </c>
-      <c r="F126" t="s">
-        <v>87</v>
+        <v>17</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G126">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B127" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C127" t="s">
         <v>6</v>
       </c>
       <c r="D127" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E127" t="s">
-        <v>20</v>
-      </c>
-      <c r="F127" t="s">
-        <v>17</v>
+        <v>58</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="G127">
-        <v>89</v>
+        <v>32</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B128" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C128" t="s">
         <v>6</v>
       </c>
       <c r="D128" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E128" t="s">
-        <v>68</v>
-      </c>
-      <c r="F128" t="s">
-        <v>66</v>
+        <v>18</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="G128">
-        <v>32</v>
+        <v>65</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B129" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C129" t="s">
         <v>6</v>
       </c>
       <c r="D129" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E129" t="s">
-        <v>21</v>
-      </c>
-      <c r="F129" t="s">
-        <v>32</v>
+        <v>18</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="G129">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B130" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C130" t="s">
         <v>6</v>
       </c>
       <c r="D130" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E130" t="s">
-        <v>21</v>
-      </c>
-      <c r="F130" t="s">
-        <v>27</v>
+        <v>13</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="G130">
-        <v>70</v>
+        <v>83</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B131" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C131" t="s">
         <v>6</v>
       </c>
       <c r="D131" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E131" t="s">
-        <v>14</v>
-      </c>
-      <c r="F131" t="s">
-        <v>13</v>
+        <v>8</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="G131">
-        <v>83</v>
+        <v>18</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B132" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C132" t="s">
         <v>6</v>
       </c>
       <c r="D132" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E132" t="s">
-        <v>8</v>
-      </c>
-      <c r="F132" t="s">
-        <v>23</v>
+        <v>13</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="G132">
-        <v>18</v>
+        <v>115</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B133" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C133" t="s">
         <v>6</v>
       </c>
       <c r="D133" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E133" t="s">
-        <v>14</v>
-      </c>
-      <c r="F133" t="s">
-        <v>31</v>
+        <v>17</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="G133">
-        <v>115</v>
+        <v>13</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B134" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C134" t="s">
         <v>6</v>
       </c>
       <c r="D134" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E134" t="s">
-        <v>20</v>
-      </c>
-      <c r="F134" t="s">
-        <v>25</v>
+        <v>18</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G134">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B135" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C135" t="s">
         <v>6</v>
       </c>
       <c r="D135" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E135" t="s">
-        <v>21</v>
-      </c>
-      <c r="F135" t="s">
-        <v>22</v>
+        <v>10</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="G135">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B136" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C136" t="s">
         <v>6</v>
       </c>
       <c r="D136" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="E136" t="s">
-        <v>11</v>
-      </c>
-      <c r="F136" t="s">
-        <v>51</v>
+        <v>65</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="G136">
-        <v>5</v>
+        <v>68</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B137" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C137" t="s">
         <v>6</v>
       </c>
       <c r="D137" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E137" t="s">
-        <v>75</v>
-      </c>
-      <c r="F137" t="s">
-        <v>76</v>
+        <v>8</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="G137">
-        <v>68</v>
+        <v>78</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B138" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C138" t="s">
         <v>6</v>
       </c>
       <c r="D138" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E138" t="s">
-        <v>8</v>
-      </c>
-      <c r="F138" t="s">
-        <v>72</v>
+        <v>95</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="G138">
-        <v>78</v>
+        <v>176</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B139" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C139" t="s">
         <v>6</v>
       </c>
       <c r="D139" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E139" t="s">
-        <v>77</v>
-      </c>
-      <c r="F139" t="s">
-        <v>78</v>
+        <v>18</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="G139">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B140" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C140" t="s">
         <v>6</v>
       </c>
       <c r="D140" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E140" t="s">
-        <v>21</v>
-      </c>
-      <c r="F140" t="s">
-        <v>27</v>
+        <v>17</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="G140">
-        <v>172</v>
+        <v>127</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B141" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C141" t="s">
         <v>6</v>
       </c>
       <c r="D141" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E141" t="s">
-        <v>20</v>
-      </c>
-      <c r="F141" t="s">
-        <v>25</v>
+        <v>17</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G141">
-        <v>127</v>
+        <v>145</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B142" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C142" t="s">
         <v>6</v>
       </c>
       <c r="D142" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E142" t="s">
-        <v>20</v>
-      </c>
-      <c r="F142" t="s">
         <v>17</v>
       </c>
+      <c r="F142" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="G142">
-        <v>145</v>
+        <v>58</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B143" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C143" t="s">
         <v>6</v>
       </c>
       <c r="D143" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E143" t="s">
-        <v>20</v>
-      </c>
-      <c r="F143" t="s">
-        <v>50</v>
+        <v>8</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="G143">
-        <v>58</v>
+        <v>77</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B144" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C144" t="s">
         <v>6</v>
       </c>
       <c r="D144" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E144" t="s">
-        <v>8</v>
-      </c>
-      <c r="F144" t="s">
-        <v>38</v>
+        <v>18</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G144">
-        <v>77</v>
+        <v>14</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B145" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C145" t="s">
         <v>6</v>
       </c>
       <c r="D145" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E145" t="s">
-        <v>21</v>
-      </c>
-      <c r="F145" t="s">
-        <v>22</v>
+        <v>13</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="G145">
-        <v>14</v>
+        <v>56</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B146" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C146" t="s">
         <v>6</v>
       </c>
       <c r="D146" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E146" t="s">
-        <v>14</v>
-      </c>
-      <c r="F146" t="s">
         <v>13</v>
       </c>
+      <c r="F146" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="G146">
-        <v>56</v>
+        <v>81</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B147" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C147" t="s">
         <v>6</v>
       </c>
       <c r="D147" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E147" t="s">
-        <v>14</v>
-      </c>
-      <c r="F147" t="s">
-        <v>60</v>
+        <v>18</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G147">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B148" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C148" t="s">
         <v>6</v>
       </c>
       <c r="D148" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E148" t="s">
-        <v>21</v>
-      </c>
-      <c r="F148" t="s">
-        <v>28</v>
+        <v>8</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="G148">
-        <v>86</v>
+        <v>118</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B149" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C149" t="s">
         <v>6</v>
       </c>
       <c r="D149" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E149" t="s">
-        <v>8</v>
-      </c>
-      <c r="F149" t="s">
-        <v>23</v>
+        <v>17</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="G149">
-        <v>118</v>
+        <v>37</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B150" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C150" t="s">
         <v>6</v>
       </c>
       <c r="D150" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E150" t="s">
-        <v>20</v>
-      </c>
-      <c r="F150" t="s">
-        <v>25</v>
+        <v>13</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="G150">
-        <v>37</v>
+        <v>218</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B151" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C151" t="s">
         <v>6</v>
       </c>
       <c r="D151" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E151" t="s">
-        <v>14</v>
-      </c>
-      <c r="F151" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="G151">
-        <v>218</v>
+        <v>49</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B152" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C152" t="s">
         <v>6</v>
       </c>
       <c r="D152" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E152" t="s">
-        <v>26</v>
-      </c>
-      <c r="F152" t="s">
-        <v>35</v>
+        <v>18</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G152">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B153" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C153" t="s">
         <v>6</v>
       </c>
       <c r="D153" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E153" t="s">
-        <v>21</v>
-      </c>
-      <c r="F153" t="s">
-        <v>28</v>
+        <v>8</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="G153">
-        <v>44</v>
+        <v>147</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B154" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C154" t="s">
         <v>6</v>
       </c>
       <c r="D154" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E154" t="s">
         <v>8</v>
       </c>
-      <c r="F154" t="s">
-        <v>81</v>
+      <c r="F154" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="G154">
-        <v>147</v>
+        <v>170</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B155" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C155" t="s">
         <v>6</v>
       </c>
       <c r="D155" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E155" t="s">
         <v>8</v>
       </c>
-      <c r="F155" t="s">
-        <v>34</v>
+      <c r="F155" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="G155">
-        <v>170</v>
+        <v>84</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B156" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C156" t="s">
         <v>6</v>
       </c>
       <c r="D156" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="E156" t="s">
         <v>8</v>
       </c>
-      <c r="F156" t="s">
-        <v>23</v>
+      <c r="F156" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="G156">
-        <v>84</v>
+        <v>18</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B157" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C157" t="s">
         <v>6</v>
       </c>
       <c r="D157" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E157" t="s">
-        <v>8</v>
-      </c>
-      <c r="F157" t="s">
-        <v>38</v>
+        <v>10</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="G157">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B158" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C158" t="s">
         <v>6</v>
       </c>
       <c r="D158" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E158" t="s">
-        <v>11</v>
-      </c>
-      <c r="F158" t="s">
-        <v>51</v>
+        <v>8</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="G158">
-        <v>12</v>
+        <v>171</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B159" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C159" t="s">
         <v>6</v>
       </c>
       <c r="D159" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E159" t="s">
-        <v>8</v>
-      </c>
-      <c r="F159" t="s">
-        <v>23</v>
+        <v>17</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="G159">
-        <v>171</v>
+        <v>135</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B160" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C160" t="s">
         <v>6</v>
       </c>
       <c r="D160" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E160" t="s">
-        <v>20</v>
-      </c>
-      <c r="F160" t="s">
-        <v>50</v>
+        <v>13</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="G160">
-        <v>135</v>
+        <v>222</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B161" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C161" t="s">
         <v>6</v>
       </c>
       <c r="D161" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E161" t="s">
-        <v>15</v>
-      </c>
-      <c r="F161" t="s">
-        <v>60</v>
+        <v>18</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G161">
-        <v>222</v>
+        <v>261</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B162" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C162" t="s">
         <v>6</v>
       </c>
       <c r="D162" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E162" t="s">
-        <v>21</v>
-      </c>
-      <c r="F162" t="s">
-        <v>28</v>
+        <v>13</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="G162">
-        <v>261</v>
+        <v>81</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B163" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C163" t="s">
         <v>6</v>
       </c>
       <c r="D163" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E163" t="s">
-        <v>14</v>
-      </c>
-      <c r="F163" t="s">
-        <v>13</v>
+        <v>18</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="G163">
-        <v>81</v>
+        <v>44</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B164" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C164" t="s">
         <v>6</v>
       </c>
       <c r="D164" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E164" t="s">
-        <v>21</v>
-      </c>
-      <c r="F164" t="s">
-        <v>24</v>
+        <v>13</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="G164">
-        <v>44</v>
+        <v>161</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B165" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C165" t="s">
         <v>6</v>
       </c>
       <c r="D165" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E165" t="s">
-        <v>14</v>
-      </c>
-      <c r="F165" t="s">
-        <v>13</v>
+        <v>18</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G165">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B166" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C166" t="s">
         <v>6</v>
       </c>
       <c r="D166" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E166" t="s">
-        <v>21</v>
-      </c>
-      <c r="F166" t="s">
+        <v>18</v>
+      </c>
+      <c r="F166" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G166">
-        <v>156</v>
+        <v>180</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B167" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C167" t="s">
         <v>6</v>
       </c>
       <c r="D167" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E167" t="s">
-        <v>21</v>
-      </c>
-      <c r="F167" t="s">
-        <v>32</v>
+        <v>13</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="G167">
-        <v>180</v>
+        <v>77</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B168" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C168" t="s">
         <v>6</v>
       </c>
       <c r="D168" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E168" t="s">
-        <v>14</v>
-      </c>
-      <c r="F168" t="s">
-        <v>29</v>
+        <v>58</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="G168">
-        <v>77</v>
+        <v>36</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B169" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C169" t="s">
         <v>6</v>
       </c>
       <c r="D169" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E169" t="s">
-        <v>68</v>
-      </c>
-      <c r="F169" t="s">
-        <v>37</v>
+        <v>18</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G169">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B170" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C170" t="s">
         <v>6</v>
       </c>
       <c r="D170" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E170" t="s">
-        <v>21</v>
-      </c>
-      <c r="F170" t="s">
-        <v>22</v>
+        <v>18</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="G170">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B171" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C171" t="s">
         <v>6</v>
       </c>
       <c r="D171" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E171" t="s">
-        <v>21</v>
-      </c>
-      <c r="F171" t="s">
-        <v>36</v>
+        <v>8</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="G171">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B172" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C172" t="s">
         <v>6</v>
       </c>
       <c r="D172" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E172" t="s">
-        <v>8</v>
-      </c>
-      <c r="F172" t="s">
-        <v>58</v>
+        <v>17</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="G172">
-        <v>14</v>
+        <v>49</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B173" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C173" t="s">
         <v>6</v>
       </c>
       <c r="D173" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E173" t="s">
-        <v>20</v>
-      </c>
-      <c r="F173" t="s">
-        <v>50</v>
+        <v>18</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="G173">
-        <v>49</v>
+        <v>128</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B174" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C174" t="s">
         <v>6</v>
       </c>
       <c r="D174" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E174" t="s">
-        <v>21</v>
-      </c>
-      <c r="F174" t="s">
-        <v>24</v>
+        <v>13</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="G174">
-        <v>128</v>
+        <v>101</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B175" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C175" t="s">
         <v>6</v>
       </c>
       <c r="D175" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E175" t="s">
-        <v>14</v>
-      </c>
-      <c r="F175" t="s">
-        <v>31</v>
+        <v>8</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="G175">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B176" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C176" t="s">
         <v>6</v>
       </c>
       <c r="D176" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="E176" t="s">
-        <v>8</v>
-      </c>
-      <c r="F176" t="s">
-        <v>84</v>
+        <v>18</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G176">
-        <v>16</v>
+        <v>33</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B177" t="s">
+        <v>5</v>
+      </c>
+      <c r="C177" t="s">
+        <v>6</v>
+      </c>
+      <c r="D177" t="s">
+        <v>74</v>
+      </c>
+      <c r="E177" t="s">
+        <v>17</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G177">
         <v>54</v>
-      </c>
-      <c r="C177" t="s">
-        <v>6</v>
-      </c>
-      <c r="D177" t="s">
-        <v>85</v>
-      </c>
-      <c r="E177" t="s">
-        <v>21</v>
-      </c>
-      <c r="F177" t="s">
-        <v>22</v>
-      </c>
-      <c r="G177">
-        <v>33</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B178" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C178" t="s">
         <v>6</v>
       </c>
       <c r="D178" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E178" t="s">
-        <v>20</v>
-      </c>
-      <c r="F178" t="s">
-        <v>50</v>
+        <v>8</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="G178">
-        <v>54</v>
+        <v>108</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B179" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C179" t="s">
         <v>6</v>
       </c>
       <c r="D179" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E179" t="s">
-        <v>8</v>
-      </c>
-      <c r="F179" t="s">
-        <v>9</v>
+        <v>13</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="G179">
-        <v>108</v>
+        <v>436</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B180" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C180" t="s">
         <v>6</v>
       </c>
       <c r="D180" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E180" t="s">
-        <v>14</v>
-      </c>
-      <c r="F180" t="s">
         <v>13</v>
       </c>
+      <c r="F180" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="G180">
-        <v>436</v>
+        <v>93</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B181" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C181" t="s">
         <v>6</v>
       </c>
       <c r="D181" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E181" t="s">
-        <v>14</v>
-      </c>
-      <c r="F181" t="s">
-        <v>31</v>
+        <v>18</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="G181">
-        <v>93</v>
+        <v>11</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B182" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C182" t="s">
         <v>6</v>
       </c>
       <c r="D182" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E182" t="s">
-        <v>21</v>
-      </c>
-      <c r="F182" t="s">
-        <v>34</v>
+        <v>13</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="G182">
-        <v>11</v>
+        <v>120</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B183" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C183" t="s">
         <v>6</v>
       </c>
       <c r="D183" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E183" t="s">
-        <v>14</v>
-      </c>
-      <c r="F183" t="s">
-        <v>13</v>
+        <v>8</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="G183">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B184" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C184" t="s">
         <v>6</v>
       </c>
       <c r="D184" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E184" t="s">
-        <v>8</v>
-      </c>
-      <c r="F184" t="s">
+        <v>13</v>
+      </c>
+      <c r="F184" s="1" t="s">
         <v>87</v>
       </c>
       <c r="G184">
-        <v>111</v>
+        <v>60</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B185" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C185" t="s">
         <v>6</v>
       </c>
       <c r="D185" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E185" t="s">
-        <v>14</v>
-      </c>
-      <c r="F185" t="s">
-        <v>60</v>
+        <v>10</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="G185">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B186" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C186" t="s">
         <v>6</v>
       </c>
       <c r="D186" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E186" t="s">
-        <v>11</v>
-      </c>
-      <c r="F186" t="s">
-        <v>51</v>
+        <v>18</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G186">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B187" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C187" t="s">
         <v>6</v>
       </c>
       <c r="D187" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E187" t="s">
-        <v>21</v>
-      </c>
-      <c r="F187" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="G187">
-        <v>44</v>
+        <v>16</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B188" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C188" t="s">
         <v>6</v>
       </c>
       <c r="D188" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E188" t="s">
-        <v>8</v>
-      </c>
-      <c r="F188" t="s">
-        <v>88</v>
+        <v>17</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="G188">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B189" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C189" t="s">
         <v>6</v>
       </c>
       <c r="D189" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E189" t="s">
-        <v>20</v>
-      </c>
-      <c r="F189" t="s">
-        <v>25</v>
+        <v>17</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="G189">
-        <v>12</v>
+        <v>56</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B190" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C190" t="s">
         <v>6</v>
       </c>
       <c r="D190" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E190" t="s">
-        <v>20</v>
-      </c>
-      <c r="F190" t="s">
-        <v>50</v>
+        <v>18</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G190">
-        <v>56</v>
+        <v>96</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B191" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C191" t="s">
         <v>6</v>
       </c>
       <c r="D191" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E191" t="s">
+        <v>18</v>
+      </c>
+      <c r="F191" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F191" t="s">
-        <v>28</v>
-      </c>
       <c r="G191">
-        <v>96</v>
+        <v>173</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B192" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C192" t="s">
         <v>6</v>
       </c>
       <c r="D192" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E192" t="s">
-        <v>21</v>
-      </c>
-      <c r="F192" t="s">
-        <v>24</v>
+        <v>13</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="G192">
-        <v>173</v>
+        <v>149</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B193" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C193" t="s">
         <v>6</v>
       </c>
       <c r="D193" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E193" t="s">
-        <v>14</v>
-      </c>
-      <c r="F193" t="s">
-        <v>31</v>
+        <v>13</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="G193">
-        <v>149</v>
+        <v>168</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B194" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C194" t="s">
         <v>6</v>
       </c>
       <c r="D194" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="E194" t="s">
-        <v>15</v>
-      </c>
-      <c r="F194" t="s">
-        <v>60</v>
+        <v>18</v>
+      </c>
+      <c r="F194" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G194">
-        <v>168</v>
+        <v>58</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B195" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C195" t="s">
         <v>6</v>
       </c>
       <c r="D195" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="E195" t="s">
-        <v>21</v>
-      </c>
-      <c r="F195" t="s">
-        <v>22</v>
+        <v>17</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G195">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B196" t="s">
+        <v>5</v>
+      </c>
+      <c r="C196" t="s">
+        <v>6</v>
+      </c>
+      <c r="D196" t="s">
+        <v>77</v>
+      </c>
+      <c r="E196" t="s">
+        <v>8</v>
+      </c>
+      <c r="F196" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G196">
         <v>54</v>
-      </c>
-      <c r="C196" t="s">
-        <v>6</v>
-      </c>
-      <c r="D196" t="s">
-        <v>89</v>
-      </c>
-      <c r="E196" t="s">
-        <v>20</v>
-      </c>
-      <c r="F196" t="s">
-        <v>17</v>
-      </c>
-      <c r="G196">
-        <v>60</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B197" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C197" t="s">
         <v>6</v>
       </c>
       <c r="D197" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="E197" t="s">
         <v>8</v>
       </c>
-      <c r="F197" t="s">
-        <v>87</v>
+      <c r="F197" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="G197">
-        <v>54</v>
+        <v>11</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B198" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C198" t="s">
         <v>6</v>
       </c>
       <c r="D198" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="E198" t="s">
-        <v>8</v>
-      </c>
-      <c r="F198" t="s">
-        <v>90</v>
+        <v>18</v>
+      </c>
+      <c r="F198" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="G198">
-        <v>11</v>
+        <v>79</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B199" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C199" t="s">
         <v>6</v>
       </c>
       <c r="D199" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="E199" t="s">
-        <v>21</v>
-      </c>
-      <c r="F199" t="s">
-        <v>24</v>
+        <v>13</v>
+      </c>
+      <c r="F199" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="G199">
-        <v>79</v>
+        <v>48</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B200" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C200" t="s">
         <v>6</v>
       </c>
       <c r="D200" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="E200" t="s">
-        <v>14</v>
-      </c>
-      <c r="F200" t="s">
-        <v>31</v>
+        <v>13</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="G200">
-        <v>48</v>
+        <v>95</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B201" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C201" t="s">
         <v>6</v>
       </c>
       <c r="D201" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="E201" t="s">
-        <v>14</v>
-      </c>
-      <c r="F201" t="s">
-        <v>13</v>
+        <v>18</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="G201">
-        <v>95</v>
+        <v>137</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B202" t="s">
+        <v>5</v>
+      </c>
+      <c r="C202" t="s">
+        <v>6</v>
+      </c>
+      <c r="D202" t="s">
+        <v>78</v>
+      </c>
+      <c r="E202" t="s">
+        <v>13</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G202">
         <v>54</v>
-      </c>
-      <c r="C202" t="s">
-        <v>6</v>
-      </c>
-      <c r="D202" t="s">
-        <v>89</v>
-      </c>
-      <c r="E202" t="s">
-        <v>21</v>
-      </c>
-      <c r="F202" t="s">
-        <v>32</v>
-      </c>
-      <c r="G202">
-        <v>137</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B203" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C203" t="s">
         <v>6</v>
       </c>
       <c r="D203" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="E203" t="s">
-        <v>15</v>
-      </c>
-      <c r="F203" t="s">
-        <v>60</v>
+        <v>18</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="G203">
-        <v>44</v>
+        <v>114</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B204" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C204" t="s">
         <v>6</v>
       </c>
       <c r="D204" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="E204" t="s">
-        <v>21</v>
-      </c>
-      <c r="F204" t="s">
-        <v>32</v>
+        <v>13</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="G204">
-        <v>114</v>
+        <v>197</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B205" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C205" t="s">
         <v>6</v>
       </c>
       <c r="D205" t="s">
+        <v>78</v>
+      </c>
+      <c r="E205" t="s">
+        <v>58</v>
+      </c>
+      <c r="F205" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E205" t="s">
-        <v>14</v>
-      </c>
-      <c r="F205" t="s">
-        <v>13</v>
-      </c>
       <c r="G205">
-        <v>197</v>
+        <v>108</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B206" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C206" t="s">
         <v>6</v>
       </c>
       <c r="D206" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="E206" t="s">
-        <v>14</v>
-      </c>
-      <c r="F206" t="s">
-        <v>60</v>
+        <v>10</v>
+      </c>
+      <c r="F206" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="G206">
-        <v>10</v>
+        <v>42</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B207" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C207" t="s">
         <v>6</v>
       </c>
       <c r="D207" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="E207" t="s">
-        <v>68</v>
-      </c>
-      <c r="F207" t="s">
-        <v>37</v>
+        <v>18</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G207">
-        <v>108</v>
+        <v>268</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B208" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C208" t="s">
         <v>6</v>
       </c>
       <c r="D208" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E208" t="s">
-        <v>11</v>
-      </c>
-      <c r="F208" t="s">
-        <v>51</v>
+        <v>8</v>
+      </c>
+      <c r="F208" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="G208">
-        <v>42</v>
+        <v>71</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B209" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C209" t="s">
         <v>6</v>
       </c>
       <c r="D209" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E209" t="s">
-        <v>21</v>
-      </c>
-      <c r="F209" t="s">
-        <v>28</v>
+        <v>13</v>
+      </c>
+      <c r="F209" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="G209">
-        <v>268</v>
+        <v>98</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B210" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C210" t="s">
         <v>6</v>
       </c>
       <c r="D210" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="E210" t="s">
         <v>8</v>
       </c>
-      <c r="F210" t="s">
-        <v>93</v>
+      <c r="F210" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="G210">
-        <v>71</v>
+        <v>51</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B211" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C211" t="s">
         <v>6</v>
       </c>
       <c r="D211" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="E211" t="s">
-        <v>14</v>
-      </c>
-      <c r="F211" t="s">
-        <v>13</v>
+        <v>18</v>
+      </c>
+      <c r="F211" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G211">
-        <v>98</v>
+        <v>209</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B212" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C212" t="s">
         <v>6</v>
       </c>
       <c r="D212" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="E212" t="s">
-        <v>8</v>
-      </c>
-      <c r="F212" t="s">
-        <v>87</v>
+        <v>13</v>
+      </c>
+      <c r="F212" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="G212">
-        <v>51</v>
+        <v>93</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B213" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C213" t="s">
         <v>6</v>
       </c>
       <c r="D213" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="E213" t="s">
-        <v>21</v>
-      </c>
-      <c r="F213" t="s">
-        <v>28</v>
+        <v>13</v>
+      </c>
+      <c r="F213" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="G213">
-        <v>209</v>
+        <v>58</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B214" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C214" t="s">
         <v>6</v>
       </c>
       <c r="D214" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="E214" t="s">
-        <v>14</v>
-      </c>
-      <c r="F214" t="s">
-        <v>29</v>
+        <v>8</v>
+      </c>
+      <c r="F214" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="G214">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B215" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C215" t="s">
         <v>6</v>
       </c>
       <c r="D215" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="E215" t="s">
-        <v>15</v>
-      </c>
-      <c r="F215" t="s">
-        <v>60</v>
+        <v>8</v>
+      </c>
+      <c r="F215" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="G215">
-        <v>58</v>
+        <v>9</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B216" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C216" t="s">
         <v>6</v>
       </c>
       <c r="D216" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="E216" t="s">
-        <v>8</v>
-      </c>
-      <c r="F216" t="s">
-        <v>93</v>
+        <v>18</v>
+      </c>
+      <c r="F216" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G216">
-        <v>87</v>
+        <v>27</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B217" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C217" t="s">
         <v>6</v>
       </c>
       <c r="D217" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="E217" t="s">
-        <v>8</v>
-      </c>
-      <c r="F217" t="s">
-        <v>9</v>
+        <v>13</v>
+      </c>
+      <c r="F217" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="G217">
-        <v>9</v>
+        <v>90</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B218" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C218" t="s">
         <v>6</v>
       </c>
       <c r="D218" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="E218" t="s">
-        <v>21</v>
-      </c>
-      <c r="F218" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="F218" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="G218">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B219" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C219" t="s">
         <v>6</v>
       </c>
       <c r="D219" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="E219" t="s">
-        <v>14</v>
-      </c>
-      <c r="F219" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F219" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="G219">
-        <v>90</v>
+        <v>37</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B220" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C220" t="s">
         <v>6</v>
       </c>
       <c r="D220" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="E220" t="s">
-        <v>70</v>
-      </c>
-      <c r="F220" t="s">
-        <v>95</v>
+        <v>13</v>
+      </c>
+      <c r="F220" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="G220">
-        <v>8</v>
+        <v>68</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B221" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C221" t="s">
         <v>6</v>
       </c>
       <c r="D221" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="E221" t="s">
+        <v>8</v>
+      </c>
+      <c r="F221" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F221" t="s">
-        <v>50</v>
-      </c>
       <c r="G221">
-        <v>37</v>
+        <v>64</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B222" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C222" t="s">
         <v>6</v>
       </c>
       <c r="D222" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="E222" t="s">
-        <v>14</v>
-      </c>
-      <c r="F222" t="s">
-        <v>31</v>
+        <v>8</v>
+      </c>
+      <c r="F222" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="G222">
-        <v>68</v>
+        <v>98</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B223" t="s">
+        <v>5</v>
+      </c>
+      <c r="C223" t="s">
+        <v>6</v>
+      </c>
+      <c r="D223" t="s">
+        <v>81</v>
+      </c>
+      <c r="E223" t="s">
+        <v>13</v>
+      </c>
+      <c r="F223" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G223">
         <v>54</v>
-      </c>
-      <c r="C223" t="s">
-        <v>6</v>
-      </c>
-      <c r="D223" t="s">
-        <v>94</v>
-      </c>
-      <c r="E223" t="s">
-        <v>8</v>
-      </c>
-      <c r="F223" t="s">
-        <v>23</v>
-      </c>
-      <c r="G223">
-        <v>64</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B224" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C224" t="s">
         <v>6</v>
       </c>
       <c r="D224" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="E224" t="s">
-        <v>8</v>
-      </c>
-      <c r="F224" t="s">
-        <v>88</v>
+        <v>17</v>
+      </c>
+      <c r="F224" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="G224">
-        <v>98</v>
+        <v>50</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B225" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C225" t="s">
         <v>6</v>
       </c>
       <c r="D225" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="E225" t="s">
-        <v>15</v>
-      </c>
-      <c r="F225" t="s">
-        <v>60</v>
+        <v>58</v>
+      </c>
+      <c r="F225" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="G225">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B226" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C226" t="s">
         <v>6</v>
       </c>
       <c r="D226" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="E226" t="s">
-        <v>20</v>
-      </c>
-      <c r="F226" t="s">
-        <v>50</v>
+        <v>8</v>
+      </c>
+      <c r="F226" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G226">
-        <v>50</v>
+        <v>169</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B227" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C227" t="s">
         <v>6</v>
       </c>
       <c r="D227" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="E227" t="s">
-        <v>68</v>
-      </c>
-      <c r="F227" t="s">
-        <v>37</v>
+        <v>8</v>
+      </c>
+      <c r="F227" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="G227">
-        <v>44</v>
+        <v>130</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B228" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C228" t="s">
         <v>6</v>
       </c>
       <c r="D228" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="E228" t="s">
-        <v>8</v>
-      </c>
-      <c r="F228" t="s">
+        <v>13</v>
+      </c>
+      <c r="F228" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G228">
         <v>43</v>
-      </c>
-      <c r="G228">
-        <v>169</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B229" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C229" t="s">
         <v>6</v>
       </c>
       <c r="D229" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="E229" t="s">
-        <v>8</v>
-      </c>
-      <c r="F229" t="s">
-        <v>81</v>
+        <v>58</v>
+      </c>
+      <c r="F229" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="G229">
-        <v>130</v>
+        <v>61</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B230" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C230" t="s">
         <v>6</v>
       </c>
       <c r="D230" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="E230" t="s">
-        <v>15</v>
-      </c>
-      <c r="F230" t="s">
-        <v>60</v>
+        <v>13</v>
+      </c>
+      <c r="F230" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="G230">
-        <v>43</v>
+        <v>112</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B231" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C231" t="s">
         <v>6</v>
       </c>
       <c r="D231" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="E231" t="s">
-        <v>68</v>
-      </c>
-      <c r="F231" t="s">
-        <v>37</v>
+        <v>8</v>
+      </c>
+      <c r="F231" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="G231">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B232" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C232" t="s">
         <v>6</v>
       </c>
       <c r="D232" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="E232" t="s">
-        <v>14</v>
-      </c>
-      <c r="F232" t="s">
-        <v>29</v>
+        <v>8</v>
+      </c>
+      <c r="F232" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="G232">
-        <v>112</v>
+        <v>9</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B233" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C233" t="s">
         <v>6</v>
       </c>
       <c r="D233" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="E233" t="s">
-        <v>8</v>
-      </c>
-      <c r="F233" t="s">
-        <v>87</v>
+        <v>17</v>
+      </c>
+      <c r="F233" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="G233">
-        <v>50</v>
+        <v>110</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B234" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C234" t="s">
         <v>6</v>
       </c>
       <c r="D234" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="E234" t="s">
-        <v>8</v>
-      </c>
-      <c r="F234" t="s">
-        <v>38</v>
+        <v>18</v>
+      </c>
+      <c r="F234" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G234">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A235" t="s">
-        <v>100</v>
-      </c>
-      <c r="B235" t="s">
-        <v>54</v>
-      </c>
-      <c r="C235" t="s">
-        <v>6</v>
-      </c>
-      <c r="D235" t="s">
-        <v>97</v>
-      </c>
-      <c r="E235" t="s">
-        <v>20</v>
-      </c>
-      <c r="F235" t="s">
-        <v>50</v>
-      </c>
-      <c r="G235">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A236" t="s">
-        <v>100</v>
-      </c>
-      <c r="B236" t="s">
-        <v>54</v>
-      </c>
-      <c r="C236" t="s">
-        <v>6</v>
-      </c>
-      <c r="D236" t="s">
-        <v>97</v>
-      </c>
-      <c r="E236" t="s">
-        <v>21</v>
-      </c>
-      <c r="F236" t="s">
-        <v>28</v>
-      </c>
-      <c r="G236">
         <v>86</v>
       </c>
     </row>

--- a/data/base de datos ordenada para procesar.xlsx
+++ b/data/base de datos ordenada para procesar.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fvygh\Documents\TESIS_PREGRADO\Heat map diversidad\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fvygh\Documents\TESIS_PREGRADO\TESIS-DE-PREGRADO\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3146813B-8734-45CC-A1F4-C2A37264F018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70D1FE6C-F09A-4C97-B2F6-E343DACE7440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{354A38B0-6B5E-400C-9BC9-4B52A0F053CA}"/>
   </bookViews>
